--- a/docs/ValueSet-retina-imaging-procedure-vs.xlsx
+++ b/docs/ValueSet-retina-imaging-procedure-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,13 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-30T22:57:21+01:00</t>
+    <t>2025-12-02</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-retina-imaging-procedure-vs.xlsx
+++ b/docs/ValueSet-retina-imaging-procedure-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/ValueSet-retina-imaging-procedure-vs.xlsx
+++ b/docs/ValueSet-retina-imaging-procedure-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.8.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/ValueSet-retina-imaging-procedure-vs.xlsx
+++ b/docs/ValueSet-retina-imaging-procedure-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.0</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/ValueSet-retina-imaging-procedure-vs.xlsx
+++ b/docs/ValueSet-retina-imaging-procedure-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/ValueSet-retina-imaging-procedure-vs.xlsx
+++ b/docs/ValueSet-retina-imaging-procedure-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
